--- a/artfynd/A 57042-2021 artfynd.xlsx
+++ b/artfynd/A 57042-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57042-2021 artfynd.xlsx
+++ b/artfynd/A 57042-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96910476</v>
+        <v>96910470</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>514334.0255863237</v>
+        <v>514404</v>
       </c>
       <c r="R2" t="n">
-        <v>6452464.717705666</v>
+        <v>6452519</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -748,19 +743,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96910479</v>
+        <v>96910471</v>
       </c>
       <c r="B3" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>514404.3414439074</v>
+        <v>514472</v>
       </c>
       <c r="R3" t="n">
-        <v>6452433.361810283</v>
+        <v>6452553</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -860,19 +840,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96910502</v>
+        <v>96910472</v>
       </c>
       <c r="B4" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>514432.5525953139</v>
+        <v>514409</v>
       </c>
       <c r="R4" t="n">
-        <v>6452368.661162325</v>
+        <v>6452471</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -972,19 +937,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,12 +969,7 @@
         <v>96910473</v>
       </c>
       <c r="B5" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>514412.9171016524</v>
+        <v>514413</v>
       </c>
       <c r="R5" t="n">
-        <v>6452397.566897816</v>
+        <v>6452397</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1084,19 +1034,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>96910500</v>
+        <v>96910474</v>
       </c>
       <c r="B6" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>514433.2644336736</v>
+        <v>514433</v>
       </c>
       <c r="R6" t="n">
-        <v>6452607.85136152</v>
+        <v>6452363</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1196,19 +1131,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>96910504</v>
+        <v>96910475</v>
       </c>
       <c r="B7" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>514429.4546592956</v>
+        <v>514431</v>
       </c>
       <c r="R7" t="n">
-        <v>6452349.682841108</v>
+        <v>6452349</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1308,19 +1228,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,53 +1257,59 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>96910501</v>
+        <v>97179241</v>
       </c>
       <c r="B8" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>241</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långstorp, Ög</t>
+          <t>SO Långkärren, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>514431.8462199402</v>
+        <v>514415</v>
       </c>
       <c r="R8" t="n">
-        <v>6452417.656340248</v>
+        <v>6452573</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1417,22 +1333,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,71 +1347,70 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>96910494</v>
+        <v>97179227</v>
       </c>
       <c r="B9" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6426</v>
+        <v>1036</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Hållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Menegazzia terebrata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Hoffm.) A.Massal.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långstorp, Ög</t>
+          <t>SO Långkärren, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>514341.2173531234</v>
+        <v>514474</v>
       </c>
       <c r="R9" t="n">
-        <v>6452373.597999355</v>
+        <v>6452629</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1434,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-11-09</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På minst 3 träd.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1553,55 +1453,51 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Andreas Larsson</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>96910495</v>
+        <v>96910479</v>
       </c>
       <c r="B10" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1507,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>514470.5801081457</v>
+        <v>514405</v>
       </c>
       <c r="R10" t="n">
-        <v>6452362.477579913</v>
+        <v>6452434</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1644,19 +1540,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1569,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>96910486</v>
+        <v>96910480</v>
       </c>
       <c r="B11" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1580,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1604,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>514408.9577484995</v>
+        <v>514324</v>
       </c>
       <c r="R11" t="n">
-        <v>6452470.258084258</v>
+        <v>6452576</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1756,19 +1637,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,37 +1666,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96910496</v>
+        <v>96910483</v>
       </c>
       <c r="B12" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1701,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>514483.2193678261</v>
+        <v>514302</v>
       </c>
       <c r="R12" t="n">
-        <v>6452370.426695137</v>
+        <v>6452445</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1868,19 +1734,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,37 +1763,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>96910497</v>
+        <v>96910484</v>
       </c>
       <c r="B13" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6426</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1798,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>514470.9732019593</v>
+        <v>514455</v>
       </c>
       <c r="R13" t="n">
-        <v>6452399.359161076</v>
+        <v>6452449</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1980,19 +1831,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,37 +1860,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>96910477</v>
+        <v>96910500</v>
       </c>
       <c r="B14" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,10 +1895,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>514298.7886620269</v>
+        <v>514433</v>
       </c>
       <c r="R14" t="n">
-        <v>6452429.291365677</v>
+        <v>6452608</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2092,19 +1928,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,37 +1957,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>96910478</v>
+        <v>96910501</v>
       </c>
       <c r="B15" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +1992,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>514431.8462199402</v>
+        <v>514432</v>
       </c>
       <c r="R15" t="n">
-        <v>6452417.656340248</v>
+        <v>6452418</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2204,19 +2025,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,37 +2054,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96910471</v>
+        <v>96910502</v>
       </c>
       <c r="B16" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2089,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>514471.9945699803</v>
+        <v>514432</v>
       </c>
       <c r="R16" t="n">
-        <v>6452553.202093521</v>
+        <v>6452369</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2316,19 +2122,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,37 +2151,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>96910470</v>
+        <v>96910503</v>
       </c>
       <c r="B17" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2395,10 +2186,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>514403.5013056031</v>
+        <v>514435</v>
       </c>
       <c r="R17" t="n">
-        <v>6452519.234733783</v>
+        <v>6452328</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2428,19 +2219,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,37 +2248,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>96910474</v>
+        <v>96910504</v>
       </c>
       <c r="B18" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2283,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>514433.6293931006</v>
+        <v>514430</v>
       </c>
       <c r="R18" t="n">
-        <v>6452362.869613292</v>
+        <v>6452350</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2540,19 +2316,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2579,37 +2345,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>96910475</v>
+        <v>96910505</v>
       </c>
       <c r="B19" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2619,10 +2380,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>514430.5141816334</v>
+        <v>514495</v>
       </c>
       <c r="R19" t="n">
-        <v>6452348.632974477</v>
+        <v>6452370</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2652,19 +2413,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2691,15 +2442,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>96910472</v>
+        <v>96910486</v>
       </c>
       <c r="B20" t="n">
-        <v>94121</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2707,21 +2453,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2731,10 +2477,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>514408.9577484995</v>
+        <v>514409</v>
       </c>
       <c r="R20" t="n">
-        <v>6452470.258084258</v>
+        <v>6452471</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2764,19 +2510,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2803,19 +2539,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>96910493</v>
+        <v>96910492</v>
       </c>
       <c r="B21" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2843,10 +2574,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>514311.1534071115</v>
+        <v>514406</v>
       </c>
       <c r="R21" t="n">
-        <v>6452367.166930206</v>
+        <v>6452658</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2876,19 +2607,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2915,37 +2636,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>96910505</v>
+        <v>96910493</v>
       </c>
       <c r="B22" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2955,10 +2671,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>514495.3635180846</v>
+        <v>514311</v>
       </c>
       <c r="R22" t="n">
-        <v>6452369.417400271</v>
+        <v>6452367</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2988,19 +2704,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3027,19 +2733,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>96910492</v>
+        <v>96910494</v>
       </c>
       <c r="B23" t="n">
-        <v>73631</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3067,10 +2768,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>514405.6383256635</v>
+        <v>514342</v>
       </c>
       <c r="R23" t="n">
-        <v>6452657.272401581</v>
+        <v>6452374</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3100,19 +2801,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3139,15 +2830,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>96910480</v>
+        <v>96910495</v>
       </c>
       <c r="B24" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3155,21 +2841,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3179,10 +2865,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>514324.1245680035</v>
+        <v>514470</v>
       </c>
       <c r="R24" t="n">
-        <v>6452575.318413283</v>
+        <v>6452362</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3212,19 +2898,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3251,15 +2927,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>96910483</v>
+        <v>96910496</v>
       </c>
       <c r="B25" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3267,21 +2938,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3291,10 +2962,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>514301.3707452905</v>
+        <v>514484</v>
       </c>
       <c r="R25" t="n">
-        <v>6452445.106235258</v>
+        <v>6452370</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3324,19 +2995,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3363,37 +3024,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>96910503</v>
+        <v>96910497</v>
       </c>
       <c r="B26" t="n">
-        <v>93276</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3403,10 +3059,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>514434.8137202156</v>
+        <v>514471</v>
       </c>
       <c r="R26" t="n">
-        <v>6452327.574047943</v>
+        <v>6452399</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3436,19 +3092,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3475,15 +3121,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>96910484</v>
+        <v>96910476</v>
       </c>
       <c r="B27" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3491,21 +3132,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3515,10 +3156,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>514455.4852344611</v>
+        <v>514334</v>
       </c>
       <c r="R27" t="n">
-        <v>6452448.826830276</v>
+        <v>6452464</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3548,19 +3189,9 @@
           <t>2021-10-24</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2021-10-24</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3587,15 +3218,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>97179241</v>
+        <v>96910477</v>
       </c>
       <c r="B28" t="n">
-        <v>83354</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3603,48 +3229,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>241</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gransotdyna</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Camarops tubulina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) Shear</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>SO Långkärren, Ög</t>
+          <t>Långstorp, Ög</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>514414.9158191551</v>
+        <v>514298</v>
       </c>
       <c r="R28" t="n">
-        <v>6452573.540495945</v>
+        <v>6452429</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3668,22 +3283,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-24</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-11-09</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-10-24</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3692,22 +3297,118 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Andreas Larsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>96910478</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Långstorp, Ög</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>514432</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6452418</v>
+      </c>
+      <c r="S29" t="n">
+        <v>15</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mjölby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Västra Harg</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2021-10-24</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2021-10-24</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Andreas Larsson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Andreas Larsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57042-2021 artfynd.xlsx
+++ b/artfynd/A 57042-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AZ29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910470</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910471</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910472</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910473</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910474</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910475</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97179241</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1469,6 +1509,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97179227</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1566,6 +1611,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910479</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1663,6 +1713,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910480</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1760,6 +1815,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910483</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1857,6 +1917,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910484</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1954,6 +2019,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910500</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2051,6 +2121,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910501</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2148,6 +2223,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910502</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2245,6 +2325,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910503</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2342,6 +2427,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910504</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2439,6 +2529,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910505</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2536,6 +2631,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910486</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2633,6 +2733,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910492</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2730,6 +2835,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910493</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2827,6 +2937,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910494</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2924,6 +3039,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910495</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3021,6 +3141,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910496</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3118,6 +3243,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910497</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3215,6 +3345,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910476</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3312,6 +3447,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910477</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3409,8 +3549,43 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96910478</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>